--- a/光伏配储项目/电价数据/2026/薄荷站.xlsx
+++ b/光伏配储项目/电价数据/2026/薄荷站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50979</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.69959</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5639400000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.50539</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.44871</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45469</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42342</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41427</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26113</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29485</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.20653</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25347</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07302</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06049</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.04679</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.02622</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.04774</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03825</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04002</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.00232</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.03799</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08565</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.02087</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.00868</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00142</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21269</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23496</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.18456</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.10581</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.02297</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01012</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.10825</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11631</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.16823</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.21781</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.16145</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.13678</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.18296</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.23456</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.20108</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.44498</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4287</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52374</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.47248</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7328600000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6099600000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.5032300000000001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.49278</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.01706</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.56933</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.53344</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.22375</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.49222</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.49561</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.59154</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.5503400000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.42944</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47943</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42139</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6184400000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.41557</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7426900000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.9873</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7991900000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5369400000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5240199999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5066499999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50544</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50234</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39381</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47436</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42297</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.51674</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.62939</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43749</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44385</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.08502999999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.25929</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.26592</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.27198</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.23897</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.5959500000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.14191</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.27086</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.24395</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.57196</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.0239</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27178</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.22773</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.16595</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.22874</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.23344</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23152</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.25028</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.23542</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.43217</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.24489</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68686</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7939299999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.78704</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.22873</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.80323</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.76683</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43544</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.58978</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43873</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43296</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40695</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33323</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51537</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.46643</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43244</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44853</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47401</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44819</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44256</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.27542</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27766</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.13378</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.27522</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.25012</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.40484</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.24054</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.26262</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.27985</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.06545999999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.20962</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.14127</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.18791</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24617</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27967</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.26749</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.27861</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.22237</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.18757</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.02515</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.27703</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.46763</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.49487</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.27511</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34339</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47028</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39022</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28169</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26307</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.21173</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.12384</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.09140999999999999</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.26606</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.22629</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.1231</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28629</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28877</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.20592</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06473000000000001</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.2601</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.20843</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04876</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.008160000000000001</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.00618</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03857</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.07238</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.10679</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.25187</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.19431</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.22295</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.18156</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.23118</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16152</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.23552</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.25174</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28594</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.39518</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.27779</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.291</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28317</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04015</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04533</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.03993</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03978</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04297</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04618</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04455</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04658</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04194</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04651</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04448</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04462</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04351</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04592</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04915</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04501</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04715999999999999</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04707</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04696</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22032</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04731</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05129</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05346</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00258</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14648</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03689</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09843</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41761</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35139</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66359</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10242</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04246</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04628</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04258</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03195</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04137</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10654</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03766</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04707</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.0421</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.0422</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04209</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04439</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0443</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04428</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04206</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0415</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04131</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03982</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04492</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04401</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.0443</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04185</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04289</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04049000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04296</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04376</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04685</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04674</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20147</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14406</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29246</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27046</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3683999999999999</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33699</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3208</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40644</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27269</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27267</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17362</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15987</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17244</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14893</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16066</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15996</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23839</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21538</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22793</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27107</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28231</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.26939</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.27186</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.41941</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.42997</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.40872</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.40551</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15736</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79111</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6218899999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49775</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78083</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.91995</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49424</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92316</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8924500000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31129</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.38184</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9154099999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63617</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.21446</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88218</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5657000000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.359</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.05219</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.55911</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.81512</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53084</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.79723</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.79679</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87975</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88654</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5158200000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.42079</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.42902</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.47583</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.23612</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87967</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55153</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6507200000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54552</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45935</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44224</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45131</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39547</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45306</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42149</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41008</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58869</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59662</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60156</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.65595</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45161</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.40636</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55821</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44639</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8619600000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6553300000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.82899</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8119700000000001</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.84829</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27115</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45289</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35338</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.98698</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.48737</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.54448</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.61253</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.41808</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.45876</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.41276</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.27769</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16456</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26083</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20054</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.25629</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27498</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.26944</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27546</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43195</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27749</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44777</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5978300000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88966</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35052</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14048</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7073200000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8000700000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6523099999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58765</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45121</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43997</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43774</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43415</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42846</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.55283</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.06219</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.57135</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.04273</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.66153</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.2188</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.5388999999999999</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26546</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26308</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26565</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40567</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.58633</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46447</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.71557</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46581</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43869</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42462</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32569</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.26322</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23584</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14494</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14726</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15412</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14438</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14079</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14415</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14261</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14469</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26673</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26711</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14214</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.03427</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11415</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11326</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14538</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14149</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14667</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45082</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44102</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44106</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44045</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44539</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44485</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4034700000000001</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35008</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54995</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46975</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41683</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.27285</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.26896</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27459</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.24334</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23876</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.18346</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.27995</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.23977</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21988</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.27399</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28682</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.28489</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.28386</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27143</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.21994</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.27971</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.27766</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.26153</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24377</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.44532</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36055</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39211</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28167</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.40974</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.27575</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26699</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03828</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25119</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25002</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.19873</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07105</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.17961</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24452</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.26825</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25003</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.28613</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29485</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41107</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46929</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.4044700000000001</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.73261</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.40913</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.45945</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.4040899999999999</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30107</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28185</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40457</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34932</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.60162</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39526</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43051</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40876</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65234</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8416</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47598</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.42032</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45977</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34505</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41162</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26075</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13405</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.28974</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28399</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.2824700000000001</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19474</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24491</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.02261</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.11354</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.02277</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.2307</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24045</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14409</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.20949</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.21691</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6549199999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.61881</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.61393</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.4682</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6363799999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47753</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.77908</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44974</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46077</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48034</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41992</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36023</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49169</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.46936</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46563</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45406</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42012</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41044</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39717</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41059</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45103</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56162</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50122</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45117</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41417</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.4045299999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.24289</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.26639</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.12627</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.00419</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.0117</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.66516</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.26805</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.08386</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.04182</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.2573</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.00711</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48582</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42881</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5085299999999999</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5102099999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.40822</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.5805</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.6989099999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.6969500000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.67461</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.76195</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5463300000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52435</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8265800000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76106</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61014</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66032</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4463</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48357</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47985</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.4737</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.53844</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42491</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44401</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45925</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43779</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42716</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44921</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41856</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45874</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40764</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39975</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27243</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15504</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40784</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45428</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46497</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.04021</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18386</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39797</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40837</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40959</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40573</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36405</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44381</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24589</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23267</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23416</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2343</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24769</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.00288</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13215</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.23237</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.01061</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.15993</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25614</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.00431</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14516</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15347</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.03006</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.0401</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21681</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22839</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.15185</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21416</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26669</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35227</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22659</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21665</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.17973</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01607</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00162</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.0429</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03352</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.0416</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.03331</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.04426</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04843</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.04151</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.16934</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21456</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27692</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24443</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24559</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.2461</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26324</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28655</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27185</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26834</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25682</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27658</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.27972</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26748</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27338</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28468</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25475</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26638</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25077</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23415</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.17793</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05504999999999999</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.40692</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.01263</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06389</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.24822</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22446</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22435</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.1434</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26934</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26085</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2431</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22141</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20568</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.18887</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21285</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22562</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.18912</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22275</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.21917</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24392</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23167</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21455</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22506</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.26848</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27051</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.2462</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24914</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18349</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06364</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.48994</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.49816</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.5463600000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.07432</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.22698</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02174</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.20189</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09293999999999999</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.007690000000000001</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20794</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.03155</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.0007099999999999999</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.04892000000000001</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02614</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.13037</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03874</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.04006000000000001</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.03257</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.08145000000000001</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02554</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.01589</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02788</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.04725</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25349</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.20863</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32531</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.1126</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27343</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.40922</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.25977</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25409</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.14059</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24444</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39247</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.11325</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25741</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26974</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.16716</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14988</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.07356</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29015</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3312</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.50681</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.50581</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25839</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.26378</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28439</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.27484</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.25934</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.16277</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26001</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.27907</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.25789</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25862</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.23669</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27535</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.26606</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.27531</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47115</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.48439</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46474</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.47739</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.03797</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40674</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.43881</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40196</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47411</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.43475</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.42057</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42583</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.7423200000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.45272</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36899</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46802</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.29115</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.20269</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.15771</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23661</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26441</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.1751</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.26807</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.27461</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43598</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39382</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56014</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.55633</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45884</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.54755</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49544</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52649</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.72985</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.77222</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54831</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5504600000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.4436</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37566</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27342</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.28019</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.25945</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.25981</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27548</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.20948</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23387</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.15481</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.02544</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.14047</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01467</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.13292</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.01165</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.04071</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02395</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23405</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.04078</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02162</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03346</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.02173</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01366</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.03022</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.12155</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.07399</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.13195</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.15762</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.19131</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.24771</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.1904</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.16144</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.22425</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.27016</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37846</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.80971</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40221</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30362</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.29342</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.25894</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.22046</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.21971</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.22407</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24266</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.08698</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01082</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.00937</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.00843</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.11821</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00552</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01533</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04424</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01217</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01593</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15564</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.17947</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.03298</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.17189</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13546</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.15592</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.18273</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.24465</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.26257</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.22654</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.26114</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44637</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39807</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.51838</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41436</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42477</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38626</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.52171</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39129</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.4197</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25425</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.21807</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.19888</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.12714</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.17603</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.20127</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.1955</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.09966</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.12565</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.05732</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.08108</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04052</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04148</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04142</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04065999999999999</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04449</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04761</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.06866999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03213000000000001</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06035</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.08356999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.14037</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.1663</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.10202</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.20804</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.18224</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.10478</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04754</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.23659</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.11886</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.10284</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.20913</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.15638</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.18654</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.20246</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.17317</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21127</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23551</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.23671</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.25336</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38853</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37279</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4947</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40717</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42987</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.4106</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.4095299999999999</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38412</v>
       </c>
     </row>
   </sheetData>
